--- a/World-Builds/Donatism/Gravity_Index.xlsx
+++ b/World-Builds/Donatism/Gravity_Index.xlsx
@@ -13,7 +13,7 @@
     <sheet name="By Cross-Check Flag" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Candidates'!$A$1:$O$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Candidates'!$A$1:$O$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Low - bare practice attested even in hostile sources' unchallenged factual reporting; persists into Gregory's 590s correspondence outside the Optatus/Augustine corpus</t>
+          <t>Low - bare practice attested directly and repeatedly in Augustine's own primary text and corroborated by Petilian's own quoted argument; Doc_01 §2 names Gregory's 590s correspondence as bearing on this specifically, but that material is unvendored and this document does not rely on it (Doc_02 §7's own discipline)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>PASS (very strong)</t>
+          <t>PASS (strong)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Passes cleanly: corroborated by Gregory's 590s correspondence, outside this world's own Author Gravity concentration</t>
+          <t>Passes: corroborated in Petilian's own quoted words (row 12) - the same hostile-text-quotes-a-Donatist-voice pattern as G1, not a source entirely outside the Optatus/Augustine corpus</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Cell 1B origin; Cell 2B ongoing; targeted directly by Cell 2A imperial policy; persists past Cell 3A's 439 close</t>
+          <t>Cell 1B origin; Cell 2B ongoing; targeted directly by Cell 2A imperial policy</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Low - four Donatist-voiced/authored texts (sermon, Passio Marculi, Macrobius's letter x2) plus independent Deo laudes epigraphy</t>
+          <t>Low - three distinct Donatist-voiced/authored texts (the sermon, Passio Marculi, Macrobius's letter to the Carthage congregation) plus independent Deo laudes epigraphy. Doc_02 §6's own 'four' figure additionally counts Tyconius's Liber Regularum, which bears on G1/interpretation, not martyr-cult specifically</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -749,12 +749,12 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Documented on largely non-hostile-mediated grounds - strongest evidentiary base of the three Primaries</t>
+          <t>Documented on largely non-hostile-mediated grounds - strongest evidentiary base of the four Primaries</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Passes most cleanly of the three Primaries: substantially attested in the Donatist-voiced/non-mediated record itself</t>
+          <t>Passes most cleanly of the four Primaries: substantially attested in the Donatist-voiced/non-mediated record itself</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -853,390 +853,467 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>D-A</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Circumcellion / Agonistici Character and Scale</t>
+          <t>Refusal of Imperial/State Religious Legitimacy</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Doc_01 §2,§5; Doc_02 §6; Doc_03 Cluster 5</t>
+          <t>Doc_01 §3,§5 (Historical Pressures, Historical Catalysts, six-cell sketch); Doc_02 §6; Doc_03 Cluster 5</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>HIGH on character/scale (Augustine/Optatus-mediated); Low on bare existence and self-designation (imperial legislation, unvendored; Augustine's report treated as reliable reportage, not independent of him)</t>
+          <t>Moderate - recurring episodes cross-corroborated even by hostile sources reporting their own side's actions; the interpretive frame ('principled refusal') rests partly on this document's own synthesis of Doc_01 §5, anchored by Donatus's own directly-quoted retort</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>PASS (recurrence only; character hostile-mediated)</t>
+          <t>PASS (strong)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>PASS (strong)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL (regional only)</t>
+          <t>PASS (strong)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>PASS (strong)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>FAILS ecology-wide; PASSES regionally (Numidia)</t>
+          <t>PASS (qualified by T1)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>PASS (narrow)</t>
+          <t>PASS (strong)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Existence/self-designation Documented; character DMR at best - sharpest divergence in this document</t>
+          <t>Recurring episodes Documented; synthesis-level interpretive frame partly this document's own reading - divergence flagged, same pattern as G1</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>FAILS strict cross-voice standard beyond bare existence and self-designation - no Donatist-voiced or non-mediated text corroborates character, scale, or conduct</t>
+          <t>Passes with qualification: Donatus's own quoted retort is a direct utterance attributed to a Donatist voice, though hostile-mediated (Optatus's own narrative frame)</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>DIVERGENT - existence Documented, character contested/DMR at best</t>
+          <t>CONSISTENT, one flagged divergence (recurring episodes vs. synthesis-level interpretive frame)</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Cell 2A (direct object of imperial legislation); Cell 2B (Maximianist suppression's reported, hostile-mediated involvement); no clean forces-connection beyond the hostile record itself</t>
+          <t>Cell 2A (oscillating imperial policy, the direct object); Cell 3A (411 Conference verdict, penal legislation, Vandal capture of Carthage removing the power this gravity refuses - the most direct forces-connection of any gravity in this document, per Doc_01 §2's own account of what 439 removes)</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Supporting, scope-qualified (Numidian regional sub-ecology only; not confirmed ecology-wide)</t>
+          <t>Primary</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>D-A</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Principled Refusal vs. Pragmatic Recourse to Imperial Power</t>
+          <t>Circumcellion / Agonistici Character and Scale</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Doc_01 §5 (Historical Pressures, Historical Catalysts, six-cell sketch); Optatus (Donatus's retort, Book III; Anulinus's relatio)</t>
+          <t>Doc_01 §2,§5; Doc_02 §6; Doc_03 Cluster 5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Each of the three named instances independently Documented; the synthesis-level characterization (principled refusal vs. pragmatic exception) is this document's own reading of Doc_01 §5</t>
+          <t>HIGH on character/scale (Augustine/Optatus-mediated). Per Doc_03's own three-way distinction: existence Low-risk (independent imperial legislation, unvendored); the agonistici self-designation term itself reaches this record only through Augustine's own report and is not evidentially on par with the independent existence claim, though treated as reliable reportage per Doc_02 §6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>PASS (three named instances)</t>
+          <t>PASS (recurrence only; character hostile-mediated)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAILS ecology-wide, PARTIAL regionally</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAILS ecology-wide, PASSES regionally</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAILS ecology-wide, PARTIAL regionally</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>PASS (spans 313-390s)</t>
+          <t>FAILS ecology-wide; PASSES regionally (Numidia)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASS (narrow)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Each instance Documented; synthesis-level characterization is this document's own reading</t>
+          <t>Existence Documented; self-designation Augustine-reported (reliable, not independent); character DMR at best - sharpest divergence in this document, across three tiers</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>Passes: each instance carries its own documentary trace (Anulinus's relatio; the Maximianist-era legal invocation), not a purely interpretive hostile characterization</t>
+          <t>FAILS strict cross-voice standard beyond bare existence and self-designation - no Donatist-voiced or non-mediated text corroborates character, scale, or conduct</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>CONSISTENT per-instance; synthesis-level framing disclosed as this document's own reading</t>
+          <t>DIVERGENT across three evidentiary tiers - existence Documented, self-designation Augustine-reported, character contested/DMR at best</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Institutional separation across three named episodes (313, 361, 390s), spanning Cells 1B through 2B</t>
+          <t>Cell 2A (direct object of imperial legislation); Cell 2B (Maximianist suppression's reported, hostile-mediated involvement); no clean forces-connection beyond the hostile record itself</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Tensional</t>
+          <t>Supporting, scope-qualified (Numidian regional sub-ecology only; not confirmed ecology-wide)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>D-B</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Purity-Rigor vs. Institutional Reception (Maximianist precedent)</t>
+          <t>Tyconius's Universalist Hermeneutics/Ecclesiology</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Doc_02 §1 (rows 3,4,47, extensively verified against On Baptism and Answer to the Letters of Petilian)</t>
+          <t>Doc_01 §4,§6; Doc_02 §1,§2,§3</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Low - the most directly and repeatedly quoted internal tension in this world's entire vendored corpus</t>
+          <t>Single-voice - visible in exactly one figure's own work and Monceaux's secondary treatment of it</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL (single voice)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>PASS (tests G1's own coherence)</t>
+          <t>FAIL (nothing else depends on it)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL (condemned, no following)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>PASS (reshapes G1, G2, G4)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Documented - most rigorously and repeatedly directly-quoted internal tension in the corpus</t>
+          <t>N/A - not tested to classification</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Passes: the Bagai and Cebarsussi sentences are quoted directly in Augustine's own primary text, not merely characterized</t>
+          <t>N/A - not tested to classification</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>CONSISTENT, no divergence</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Cell 2B - the Maximianist fracture (393-398), internal to G4's own conciliar machinery</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Tensional</t>
+          <t>Not a gravity</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>D-B</t>
+          <t>D-C</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Tyconius's Universalist Hermeneutics/Ecclesiology</t>
+          <t>Numidian Native-Social-Protest Substrate</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Doc_01 §4,§6; Doc_02 §1,§2,§3</t>
+          <t>Doc_02 §5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Single-voice - visible in exactly one figure's own work and Monceaux's secondary treatment of it</t>
+          <t>Confidence C, contested even in the secondary scholarship consulted (Frend vs. Shaw/Brown)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>FAIL (single voice)</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>FAIL (nothing else depends on it)</t>
+          <t>Not tested</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Confidence C, unresolved contest in Doc_02 §5 itself</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Not tested</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>N/A - too evidentially unsettled to test</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>FAIL (condemned, no following)</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>N/A - not tested to classification</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>N/A - not tested to classification</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Not a gravity</t>
+          <t>Not tested</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>D-C</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Numidian Native-Social-Protest Substrate</t>
+          <t>Principled Refusal vs. Pragmatic Recourse to Imperial Power</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Doc_02 §5</t>
+          <t>Doc_01 §5 (Historical Pressures, Historical Catalysts, six-cell sketch); Optatus (Donatus's retort, Book III; Anulinus's relatio). Surfaced testing G5's own Persistence; generation entry added per Framework discipline</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Confidence C, contested even in the secondary scholarship consulted (Frend vs. Shaw/Brown)</t>
+          <t>Each of the three named instances independently Documented; the synthesis-level characterization (principled refusal vs. pragmatic exception) is this document's own reading of Doc_01 §5</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>PASS (three named instances)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>PASS (spans 313-390s)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Confidence C, unresolved contest in Doc_02 §5 itself</t>
+          <t>Each instance Documented; synthesis-level characterization is this document's own reading</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Passes: each instance carries its own documentary trace (Anulinus's relatio; the Maximianist-era legal invocation), not a purely interpretive hostile characterization</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>N/A - too evidentially unsettled to test</t>
+          <t>CONSISTENT per-instance; synthesis-level framing disclosed as this document's own reading</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Institutional separation across three named episodes (313, 361, 390s), spanning Cells 1B through 2B</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
+          <t>Tensional</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Purity-Rigor vs. Institutional Reception (Maximianist precedent)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Doc_02 §1 (rows 3,4,47, extensively verified against On Baptism and Answer to the Letters of Petilian). Surfaced testing G1's own internal consistency; generation entry added per Framework discipline</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Low - the most directly and repeatedly quoted internal tension in this world's entire vendored corpus</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>PASS (tests G1's own coherence)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>PASS (reshapes G1, G2, G4)</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Documented - most rigorously and repeatedly directly-quoted internal tension in the corpus</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Passes: the Bagai and Cebarsussi sentences are quoted directly in Augustine's own primary text, not merely characterized</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>CONSISTENT, no divergence</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Cell 2B - the Maximianist fracture (393-398), internal to G4's own conciliar machinery</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>Tensional</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O10"/>
+  <autoFilter ref="A1:O11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1247,7 +1324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1258,6 +1335,7 @@
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1288,15 +1366,20 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
           <t>D-A</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>T1</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>T2</t>
         </is>
@@ -1330,15 +1413,20 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1372,15 +1460,20 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1414,15 +1507,20 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
       <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -1456,15 +1554,20 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1473,49 +1576,54 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>D-A</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>R</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>D-A</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -1530,7 +1638,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>–</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1550,56 +1658,113 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
           <t>T2</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Legend: R reinforcing, C competing, X reshaping, – no demonstrated relationship. G5 (Refusal of Imperial Legitimacy) is represented through T1, its own named internal qualification (Doc_04 §3.6); see Doc_04 §6 for G5's own prose-level pairwise relationships.</t>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Legend: R reinforcing, C competing, X reshaping, – no demonstrated relationship. Every candidate row has at least one demonstrated relationship (Framework Part III's own red-flag check).</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -1693,51 +1858,51 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Supporting (integrating/institutional center)</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>G4</t>
+          <t>G5</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Parallel Institutional Hierarchy</t>
+          <t>Refusal of Imperial/State Religious Legitimacy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Supporting, scope-qualified (Numidian regional sub-ecology only; not confirmed ecology-wide)</t>
+          <t>Supporting (integrating/institutional center)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>D-A</t>
+          <t>G4</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Circumcellion / Agonistici Character and Scale</t>
+          <t>Parallel Institutional Hierarchy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Tensional</t>
+          <t>Supporting, scope-qualified (Numidian regional sub-ecology only; not confirmed ecology-wide)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>D-A</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Principled Refusal vs. Pragmatic Recourse to Imperial Power</t>
+          <t>Circumcellion / Agonistici Character and Scale</t>
         </is>
       </c>
     </row>
@@ -1749,80 +1914,87 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Purity-Rigor vs. Institutional Reception (Maximianist precedent)</t>
+          <t>Principled Refusal vs. Pragmatic Recourse to Imperial Power</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Not a gravity</t>
+          <t>Tensional</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>D-B</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Tyconius's Universalist Hermeneutics/Ecclesiology</t>
+          <t>Purity-Rigor vs. Institutional Reception (Maximianist precedent)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>Not a gravity</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>D-B</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Tyconius's Universalist Hermeneutics/Ecclesiology</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
           <t>Not tested</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>D-C</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Numidian Native-Social-Protest Substrate</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Counts</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Supporting</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Tensional</t>
+          <t>Supporting</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
@@ -1832,10 +2004,20 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>Tensional</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>Not advanced</t>
         </is>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B17" s="5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1850,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1902,17 +2084,34 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Refusal of Imperial/State Religious Legitimacy</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>The recurring historical episodes (313/314 rulings and their rejection, the Macarian repression, the 405 Edict, the 411 Conference) are Documented, cross-corroborated even by hostile sources. The synthesis-level interpretive frame - that these episodes together constitute a principled refusal of the state's own adjudicating authority - is partly this document's own reading of Doc_01 §5, corroborated by one direct quoted utterance (Donatus's own retort) but not itself an independently-attested Donatist self-description of the pattern as a whole. Named, not resolved by treating the synthesis as equivalent to a settled Donatist doctrine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>D-A</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Circumcellion / Agonistici Character and Scale</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>The sharpest divergence in this document: bare existence and self-designation are Documented (imperial legislation, though unvendored; Augustine's report of the self-designation treated as reliable reportage). Character, scale, and typical conduct rest on hostile-mediated characterization and reach at most Dominant Modern Reconstruction on Shaw's corrective reading. Classified Supporting and scope-qualified (Numidian regional sub-ecology only) rather than upgraded on the strength of the hostile portrait's vividness.</t>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>The sharpest divergence in this document, across three evidentiary tiers, not two: bare existence is Documented (imperial legislation, though unvendored); the agonistici self-designation term itself is Augustine-reported (treated as reliable reportage per Doc_02 §6, but not evidentially independent of him); character, scale, and typical conduct rest on hostile-mediated characterization and reach at most Dominant Modern Reconstruction on Shaw's corrective reading. Classified Supporting and scope-qualified (Numidian regional sub-ecology only) rather than upgraded on the strength of the hostile portrait's vividness.</t>
         </is>
       </c>
     </row>

--- a/World-Builds/Donatism/Gravity_Index.xlsx
+++ b/World-Builds/Donatism/Gravity_Index.xlsx
@@ -1517,7 +1517,7 @@
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>–</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>–</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>–</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
